--- a/cod_estandard.xlsx
+++ b/cod_estandard.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="کدینگ استاندارد حسابداری" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سرفصل کامل تر" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +36,31 @@
       <name val="Tahoma"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="IRANSans"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="IRANSans"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="IRANSans"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="IRANSans"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -115,8 +139,26 @@
         <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,11 +180,25 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +268,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3954,4 +4031,6032 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H154"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>کد گروه</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>عنوان گروه حساب</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>کد کل</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>عنوان حساب کل</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>کد معین</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>عنوان حساب معین</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>ماهیت حساب</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>سطح</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr"/>
+      <c r="D2" s="26" t="inlineStr"/>
+      <c r="E2" s="25" t="inlineStr"/>
+      <c r="F2" s="26" t="inlineStr"/>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H2" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr"/>
+      <c r="F3" s="28" t="inlineStr"/>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>110101</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>صندوق‌ها</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>110102</t>
+        </is>
+      </c>
+      <c r="F5" s="30" t="inlineStr">
+        <is>
+          <t>بانک‌های ریالی</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>110103</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>بانک‌های ارزی</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>110104</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>تنخواه‌گردان‌ها</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>موجودی نقد و بانک</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>110105</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>وجوه در راه</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های کوتاه مدت</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr"/>
+      <c r="F9" s="28" t="inlineStr"/>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های کوتاه مدت</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>110201</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>سپرده‌های بانکی کوتاه مدت</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های کوتاه مدت</t>
+        </is>
+      </c>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>110202</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>سهام و اوراق بهادار کوتاه مدت</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr"/>
+      <c r="F12" s="28" t="inlineStr"/>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>110301</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های دریافتنی (مشتریان تجاری)</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>110302</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>اسناد دریافتنی نزد صندوق</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>110303</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>اسناد دریافتنی در جریان وصول</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>110304</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>اسناد واخواست شده</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد دریافتنی تجاری</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>110305</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>ذخیره مطالبات مشکوک‌الوصول</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr"/>
+      <c r="F18" s="28" t="inlineStr"/>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>110401</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>مساعده حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E20" s="29" t="inlineStr">
+        <is>
+          <t>110402</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>وام و مطالبات پرسنل</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>110403</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>سپرده‌های دریافتنی (ودیعه)</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>110404</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>مطالبات از شرکت‌های وابسته</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد دریافتنی</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>110405</t>
+        </is>
+      </c>
+      <c r="F23" s="30" t="inlineStr">
+        <is>
+          <t>جاری شرکا (بدهکار)</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr"/>
+      <c r="F24" s="28" t="inlineStr"/>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>110501</t>
+        </is>
+      </c>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>موجودی کالا در انبار</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>110502</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد اولیه</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>110503</t>
+        </is>
+      </c>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>موجودی قطعات و ملزومات</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>110504</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>کالای در جریان ساخت</t>
+        </is>
+      </c>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>110505</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>کالای ساخته شده</t>
+        </is>
+      </c>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>موجودی مواد و کالا</t>
+        </is>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>110506</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>کالای امانی نزد دیگران</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H30" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت‌ها</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr"/>
+      <c r="F31" s="28" t="inlineStr"/>
+      <c r="G31" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H31" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت‌ها</t>
+        </is>
+      </c>
+      <c r="E32" s="29" t="inlineStr">
+        <is>
+          <t>110601</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت خرید مواد و کالا</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H32" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت‌ها</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>110602</t>
+        </is>
+      </c>
+      <c r="F33" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت اجاره</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H33" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت‌ها</t>
+        </is>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
+        <is>
+          <t>110603</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت بیمه</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H34" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای جاری</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت‌ها</t>
+        </is>
+      </c>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>110604</t>
+        </is>
+      </c>
+      <c r="F35" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌پرداخت تبلیغات</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H35" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr"/>
+      <c r="D36" s="26" t="inlineStr"/>
+      <c r="E36" s="25" t="inlineStr"/>
+      <c r="F36" s="26" t="inlineStr"/>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr"/>
+      <c r="F37" s="28" t="inlineStr"/>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H37" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D38" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>120101</t>
+        </is>
+      </c>
+      <c r="F38" s="30" t="inlineStr">
+        <is>
+          <t>زمین</t>
+        </is>
+      </c>
+      <c r="G38" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E39" s="29" t="inlineStr">
+        <is>
+          <t>120102</t>
+        </is>
+      </c>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>ساختمان و تاسیسات</t>
+        </is>
+      </c>
+      <c r="G39" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H39" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E40" s="29" t="inlineStr">
+        <is>
+          <t>120103</t>
+        </is>
+      </c>
+      <c r="F40" s="30" t="inlineStr">
+        <is>
+          <t>ماشین‌آلات و تجهیزات</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H40" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E41" s="29" t="inlineStr">
+        <is>
+          <t>120104</t>
+        </is>
+      </c>
+      <c r="F41" s="30" t="inlineStr">
+        <is>
+          <t>وسایط نقلیه</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H41" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A42" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E42" s="29" t="inlineStr">
+        <is>
+          <t>120105</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>اثاثه و منصوبات</t>
+        </is>
+      </c>
+      <c r="G42" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H42" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="D43" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>120106</t>
+        </is>
+      </c>
+      <c r="F43" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های ثابت در جریان تکمیل</t>
+        </is>
+      </c>
+      <c r="G43" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H43" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D44" s="28" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr"/>
+      <c r="F44" s="28" t="inlineStr"/>
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H44" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D45" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="E45" s="29" t="inlineStr">
+        <is>
+          <t>120201</t>
+        </is>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته ساختمان</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H45" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A46" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="inlineStr">
+        <is>
+          <t>120202</t>
+        </is>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته ماشین‌آلات</t>
+        </is>
+      </c>
+      <c r="G46" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H46" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C47" s="29" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="E47" s="29" t="inlineStr">
+        <is>
+          <t>120203</t>
+        </is>
+      </c>
+      <c r="F47" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته وسایط نقلیه</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H47" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>120204</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>استهلاک انباشته اثاثه</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H48" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>دارایی‌های نامشهود</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr"/>
+      <c r="F49" s="28" t="inlineStr"/>
+      <c r="G49" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H49" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C50" s="29" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های نامشهود</t>
+        </is>
+      </c>
+      <c r="E50" s="29" t="inlineStr">
+        <is>
+          <t>120301</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>نرم‌افزارهای رایانه‌ای</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H50" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B51" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C51" s="29" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="D51" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های نامشهود</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
+        <is>
+          <t>120302</t>
+        </is>
+      </c>
+      <c r="F51" s="30" t="inlineStr">
+        <is>
+          <t>حق‌الامتیاز و علائم تجاری</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H51" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>دارایی‌های نامشهود</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>سرقفلی</t>
+        </is>
+      </c>
+      <c r="G52" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H52" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="D53" s="28" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های بلندمدت</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr"/>
+      <c r="F53" s="28" t="inlineStr"/>
+      <c r="G53" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H53" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A54" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های بلندمدت</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>120401</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>سهام شرکت‌های وابسته و فرعی</t>
+        </is>
+      </c>
+      <c r="G54" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H54" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A55" s="29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="inlineStr">
+        <is>
+          <t>دارائیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C55" s="29" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه‌گذاری‌های بلندمدت</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>120402</t>
+        </is>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>سپرده‌های بلندمدت بانکی</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H55" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr"/>
+      <c r="D56" s="26" t="inlineStr"/>
+      <c r="E56" s="25" t="inlineStr"/>
+      <c r="F56" s="26" t="inlineStr"/>
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H56" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="D57" s="28" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد پرداختنی تجاری</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr"/>
+      <c r="F57" s="28" t="inlineStr"/>
+      <c r="G57" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H57" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C58" s="29" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد پرداختنی تجاری</t>
+        </is>
+      </c>
+      <c r="E58" s="29" t="inlineStr">
+        <is>
+          <t>210101</t>
+        </is>
+      </c>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های پرداختنی (تامین‌کنندگان داخلی)</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H58" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد پرداختنی تجاری</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>210102</t>
+        </is>
+      </c>
+      <c r="F59" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های پرداختنی (تامین‌کنندگان خارجی)</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H59" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌ها و اسناد پرداختنی تجاری</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>210103</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>اسناد پرداختنی عهده بانک‌ها</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr"/>
+      <c r="F61" s="28" t="inlineStr"/>
+      <c r="G61" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H61" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E62" s="29" t="inlineStr">
+        <is>
+          <t>210201</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>حقوق و دستمزد پرداختنی</t>
+        </is>
+      </c>
+      <c r="G62" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H62" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D63" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E63" s="29" t="inlineStr">
+        <is>
+          <t>210202</t>
+        </is>
+      </c>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>بیمه پرداختنی (سازمان تامین اجتماعی)</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H63" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C64" s="29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E64" s="29" t="inlineStr">
+        <is>
+          <t>210203</t>
+        </is>
+      </c>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>مالیات تکلیفی و حقوق پرداختنی</t>
+        </is>
+      </c>
+      <c r="G64" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H64" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C65" s="29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E65" s="29" t="inlineStr">
+        <is>
+          <t>210204</t>
+        </is>
+      </c>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>مالیات بر ارزش افزوده پرداختنی</t>
+        </is>
+      </c>
+      <c r="G65" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H65" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>سایر حساب‌ها و اسناد پرداختنی</t>
+        </is>
+      </c>
+      <c r="E66" s="29" t="inlineStr">
+        <is>
+          <t>210205</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>جاری شرکا (بستانکار)</t>
+        </is>
+      </c>
+      <c r="G66" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H66" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B67" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D67" s="28" t="inlineStr">
+        <is>
+          <t>پیش‌دریافت‌ها</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="inlineStr"/>
+      <c r="F67" s="28" t="inlineStr"/>
+      <c r="G67" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H67" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌دریافت‌ها</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>210301</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>پیش‌دریافت از مشتریان</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B69" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C69" s="27" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D69" s="28" t="inlineStr">
+        <is>
+          <t>ذخایر جاری</t>
+        </is>
+      </c>
+      <c r="E69" s="27" t="inlineStr"/>
+      <c r="F69" s="28" t="inlineStr"/>
+      <c r="G69" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H69" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A70" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C70" s="29" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>ذخایر جاری</t>
+        </is>
+      </c>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>210401</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>ذخیره مالیات بر درآمد</t>
+        </is>
+      </c>
+      <c r="G70" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H70" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B71" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C71" s="29" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D71" s="30" t="inlineStr">
+        <is>
+          <t>ذخایر جاری</t>
+        </is>
+      </c>
+      <c r="E71" s="29" t="inlineStr">
+        <is>
+          <t>210402</t>
+        </is>
+      </c>
+      <c r="F71" s="30" t="inlineStr">
+        <is>
+          <t>ذخیره بازخرید مرخصی</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H71" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C72" s="27" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D72" s="28" t="inlineStr">
+        <is>
+          <t>تسهیلات مالی کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="E72" s="27" t="inlineStr"/>
+      <c r="F72" s="28" t="inlineStr"/>
+      <c r="G72" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H72" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>تسهیلات مالی کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>210501</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>وام‌ها و تسهیلات بانکی کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="G73" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای جاری</t>
+        </is>
+      </c>
+      <c r="C74" s="29" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>تسهیلات مالی کوتاه‌مدت</t>
+        </is>
+      </c>
+      <c r="E74" s="29" t="inlineStr">
+        <is>
+          <t>210502</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>حصه جاری تسهیلات بلندمدت</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H74" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>بدهیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="inlineStr"/>
+      <c r="D75" s="26" t="inlineStr"/>
+      <c r="E75" s="25" t="inlineStr"/>
+      <c r="F75" s="26" t="inlineStr"/>
+      <c r="G75" s="25" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H75" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B76" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C76" s="27" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="D76" s="28" t="inlineStr">
+        <is>
+          <t>تسهیلات مالی بلندمدت</t>
+        </is>
+      </c>
+      <c r="E76" s="27" t="inlineStr"/>
+      <c r="F76" s="28" t="inlineStr"/>
+      <c r="G76" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H76" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>تسهیلات مالی بلندمدت</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>220101</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>وام‌ها و تسهیلات بانکی بلندمدت</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
+        <is>
+          <t>بدهیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C78" s="27" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D78" s="28" t="inlineStr">
+        <is>
+          <t>ذخیره مزایای پایان خدمت پرسنل</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr"/>
+      <c r="F78" s="28" t="inlineStr"/>
+      <c r="G78" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A79" s="29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B79" s="30" t="inlineStr">
+        <is>
+          <t>بدهیهای غیرجاری</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="D79" s="30" t="inlineStr">
+        <is>
+          <t>ذخیره مزایای پایان خدمت پرسنل</t>
+        </is>
+      </c>
+      <c r="E79" s="29" t="inlineStr">
+        <is>
+          <t>220201</t>
+        </is>
+      </c>
+      <c r="F79" s="30" t="inlineStr">
+        <is>
+          <t>ذخیره بازخرید سنوات خدمت</t>
+        </is>
+      </c>
+      <c r="G79" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H79" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="inlineStr"/>
+      <c r="D80" s="26" t="inlineStr"/>
+      <c r="E80" s="25" t="inlineStr"/>
+      <c r="F80" s="26" t="inlineStr"/>
+      <c r="G80" s="25" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H80" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B81" s="28" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C81" s="27" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="D81" s="28" t="inlineStr">
+        <is>
+          <t>سرمایه</t>
+        </is>
+      </c>
+      <c r="E81" s="27" t="inlineStr"/>
+      <c r="F81" s="28" t="inlineStr"/>
+      <c r="G81" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H81" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A82" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B82" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="D82" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه</t>
+        </is>
+      </c>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>310101</t>
+        </is>
+      </c>
+      <c r="F82" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه ثبت شده</t>
+        </is>
+      </c>
+      <c r="G82" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H82" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B83" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="D83" s="30" t="inlineStr">
+        <is>
+          <t>سرمایه</t>
+        </is>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>310102</t>
+        </is>
+      </c>
+      <c r="F83" s="30" t="inlineStr">
+        <is>
+          <t>افزایش سرمایه در جریان ثبت</t>
+        </is>
+      </c>
+      <c r="G83" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H83" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="D84" s="28" t="inlineStr">
+        <is>
+          <t>اندوخته‌ها</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr"/>
+      <c r="F84" s="28" t="inlineStr"/>
+      <c r="G84" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H84" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B85" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="D85" s="30" t="inlineStr">
+        <is>
+          <t>اندوخته‌ها</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>310201</t>
+        </is>
+      </c>
+      <c r="F85" s="30" t="inlineStr">
+        <is>
+          <t>اندوخته قانونی</t>
+        </is>
+      </c>
+      <c r="G85" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H85" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B86" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="D86" s="30" t="inlineStr">
+        <is>
+          <t>اندوخته‌ها</t>
+        </is>
+      </c>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>310202</t>
+        </is>
+      </c>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <t>اندوخته عمومی و احتیاطی</t>
+        </is>
+      </c>
+      <c r="G86" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H86" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B87" s="28" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="D87" s="28" t="inlineStr">
+        <is>
+          <t>سود و زیان انباشته</t>
+        </is>
+      </c>
+      <c r="E87" s="27" t="inlineStr"/>
+      <c r="F87" s="28" t="inlineStr"/>
+      <c r="G87" s="27" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H87" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A88" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C88" s="29" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>سود و زیان انباشته</t>
+        </is>
+      </c>
+      <c r="E88" s="29" t="inlineStr">
+        <is>
+          <t>310301</t>
+        </is>
+      </c>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>سود (زیان) انباشته</t>
+        </is>
+      </c>
+      <c r="G88" s="29" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H88" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D89" s="28" t="inlineStr">
+        <is>
+          <t>برداشت‌ها و تقسیم سود</t>
+        </is>
+      </c>
+      <c r="E89" s="27" t="inlineStr"/>
+      <c r="F89" s="28" t="inlineStr"/>
+      <c r="G89" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H89" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>حقوق صاحبان سهام</t>
+        </is>
+      </c>
+      <c r="C90" s="29" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>برداشت‌ها و تقسیم سود</t>
+        </is>
+      </c>
+      <c r="E90" s="29" t="inlineStr">
+        <is>
+          <t>310401</t>
+        </is>
+      </c>
+      <c r="F90" s="30" t="inlineStr">
+        <is>
+          <t>سود پیشنهادی و مصوب</t>
+        </is>
+      </c>
+      <c r="G90" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H90" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B91" s="26" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr"/>
+      <c r="D91" s="26" t="inlineStr"/>
+      <c r="E91" s="25" t="inlineStr"/>
+      <c r="F91" s="26" t="inlineStr"/>
+      <c r="G91" s="25" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr"/>
+      <c r="F92" s="28" t="inlineStr"/>
+      <c r="G92" s="27" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H92" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A93" s="29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B93" s="30" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C93" s="29" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D93" s="30" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E93" s="29" t="inlineStr">
+        <is>
+          <t>410101</t>
+        </is>
+      </c>
+      <c r="F93" s="30" t="inlineStr">
+        <is>
+          <t>درآمد حاصل از سود سپرده‌های بانکی</t>
+        </is>
+      </c>
+      <c r="G93" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H93" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A94" s="29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B94" s="30" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C94" s="29" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E94" s="29" t="inlineStr">
+        <is>
+          <t>410102</t>
+        </is>
+      </c>
+      <c r="F94" s="30" t="inlineStr">
+        <is>
+          <t>سود (زیان) حاصل از فروش دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="G94" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H94" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A95" s="29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B95" s="30" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C95" s="29" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D95" s="30" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E95" s="29" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="F95" s="30" t="inlineStr">
+        <is>
+          <t>سود حاصل از فروش سرمایه‌گذاری‌ها</t>
+        </is>
+      </c>
+      <c r="G95" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H95" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A96" s="29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B96" s="30" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C96" s="29" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D96" s="30" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E96" s="29" t="inlineStr">
+        <is>
+          <t>410104</t>
+        </is>
+      </c>
+      <c r="F96" s="30" t="inlineStr">
+        <is>
+          <t>سود حاصل از تسعیر ارز غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="G96" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H96" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A97" s="29" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B97" s="30" t="inlineStr">
+        <is>
+          <t>درآمدها</t>
+        </is>
+      </c>
+      <c r="C97" s="29" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D97" s="30" t="inlineStr">
+        <is>
+          <t>درآمدهای غیرعملیاتی</t>
+        </is>
+      </c>
+      <c r="E97" s="29" t="inlineStr">
+        <is>
+          <t>410105</t>
+        </is>
+      </c>
+      <c r="F97" s="30" t="inlineStr">
+        <is>
+          <t>سایر درآمدهای متفرقه</t>
+        </is>
+      </c>
+      <c r="G97" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B98" s="26" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C98" s="25" t="inlineStr"/>
+      <c r="D98" s="26" t="inlineStr"/>
+      <c r="E98" s="25" t="inlineStr"/>
+      <c r="F98" s="26" t="inlineStr"/>
+      <c r="G98" s="25" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H98" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B99" s="28" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C99" s="27" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="D99" s="28" t="inlineStr">
+        <is>
+          <t>فروش کالا و خدمات</t>
+        </is>
+      </c>
+      <c r="E99" s="27" t="inlineStr"/>
+      <c r="F99" s="28" t="inlineStr"/>
+      <c r="G99" s="27" t="inlineStr">
+        <is>
+          <t>bستانکار</t>
+        </is>
+      </c>
+      <c r="H99" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A100" s="29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B100" s="30" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C100" s="29" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="D100" s="30" t="inlineStr">
+        <is>
+          <t>فروش کالا و خدمات</t>
+        </is>
+      </c>
+      <c r="E100" s="29" t="inlineStr">
+        <is>
+          <t>420101</t>
+        </is>
+      </c>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <t>فروش ناخالص کالا (داخلی)</t>
+        </is>
+      </c>
+      <c r="G100" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H100" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A101" s="29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B101" s="30" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C101" s="29" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="D101" s="30" t="inlineStr">
+        <is>
+          <t>فروش کالا و خدمات</t>
+        </is>
+      </c>
+      <c r="E101" s="29" t="inlineStr">
+        <is>
+          <t>420102</t>
+        </is>
+      </c>
+      <c r="F101" s="30" t="inlineStr">
+        <is>
+          <t>فروش ناخالص کالا (صادراتی)</t>
+        </is>
+      </c>
+      <c r="G101" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H101" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A102" s="29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B102" s="30" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C102" s="29" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="D102" s="30" t="inlineStr">
+        <is>
+          <t>فروش کالا و خدمات</t>
+        </is>
+      </c>
+      <c r="E102" s="29" t="inlineStr">
+        <is>
+          <t>420103</t>
+        </is>
+      </c>
+      <c r="F102" s="30" t="inlineStr">
+        <is>
+          <t>درآمد حاصل از ارائه خدمات</t>
+        </is>
+      </c>
+      <c r="G102" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H102" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B103" s="28" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="D103" s="28" t="inlineStr">
+        <is>
+          <t>برگشت از فروش و تخفیفات</t>
+        </is>
+      </c>
+      <c r="E103" s="27" t="inlineStr"/>
+      <c r="F103" s="28" t="inlineStr"/>
+      <c r="G103" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H103" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A104" s="29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B104" s="30" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C104" s="29" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="D104" s="30" t="inlineStr">
+        <is>
+          <t>برگشت از فروش و تخفیفات</t>
+        </is>
+      </c>
+      <c r="E104" s="29" t="inlineStr">
+        <is>
+          <t>420201</t>
+        </is>
+      </c>
+      <c r="F104" s="30" t="inlineStr">
+        <is>
+          <t>برگشت از فروش و کاهش قیمت</t>
+        </is>
+      </c>
+      <c r="G104" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H104" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A105" s="29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B105" s="30" t="inlineStr">
+        <is>
+          <t>فروش</t>
+        </is>
+      </c>
+      <c r="C105" s="29" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="D105" s="30" t="inlineStr">
+        <is>
+          <t>برگشت از فروش و تخفیفات</t>
+        </is>
+      </c>
+      <c r="E105" s="29" t="inlineStr">
+        <is>
+          <t>420202</t>
+        </is>
+      </c>
+      <c r="F105" s="30" t="inlineStr">
+        <is>
+          <t>تخفیفات نقدی فروش</t>
+        </is>
+      </c>
+      <c r="G105" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H105" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="25" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B106" s="26" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C106" s="25" t="inlineStr"/>
+      <c r="D106" s="26" t="inlineStr"/>
+      <c r="E106" s="25" t="inlineStr"/>
+      <c r="F106" s="26" t="inlineStr"/>
+      <c r="G106" s="25" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H106" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B107" s="28" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C107" s="27" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="D107" s="28" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="E107" s="27" t="inlineStr"/>
+      <c r="F107" s="28" t="inlineStr"/>
+      <c r="G107" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H107" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A108" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C108" s="29" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="D108" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="E108" s="29" t="inlineStr">
+        <is>
+          <t>510101</t>
+        </is>
+      </c>
+      <c r="F108" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای خریداری/ساخته شده</t>
+        </is>
+      </c>
+      <c r="G108" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H108" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A109" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B109" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C109" s="29" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="D109" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="E109" s="29" t="inlineStr">
+        <is>
+          <t>510102</t>
+        </is>
+      </c>
+      <c r="F109" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده خدمات ارائه شده</t>
+        </is>
+      </c>
+      <c r="G109" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H109" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B110" s="28" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C110" s="27" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="D110" s="28" t="inlineStr">
+        <is>
+          <t>خرید و ملزومات</t>
+        </is>
+      </c>
+      <c r="E110" s="27" t="inlineStr"/>
+      <c r="F110" s="28" t="inlineStr"/>
+      <c r="G110" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H110" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A111" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B111" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C111" s="29" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="D111" s="30" t="inlineStr">
+        <is>
+          <t>خرید و ملزومات</t>
+        </is>
+      </c>
+      <c r="E111" s="29" t="inlineStr">
+        <is>
+          <t>510201</t>
+        </is>
+      </c>
+      <c r="F111" s="30" t="inlineStr">
+        <is>
+          <t>خرید ناخالص کالا</t>
+        </is>
+      </c>
+      <c r="G111" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H111" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A112" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B112" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C112" s="29" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="D112" s="30" t="inlineStr">
+        <is>
+          <t>خرید و ملزومات</t>
+        </is>
+      </c>
+      <c r="E112" s="29" t="inlineStr">
+        <is>
+          <t>510202</t>
+        </is>
+      </c>
+      <c r="F112" s="30" t="inlineStr">
+        <is>
+          <t>برگشت از خرید و تخفیفات</t>
+        </is>
+      </c>
+      <c r="G112" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H112" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A113" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B113" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C113" s="29" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="D113" s="30" t="inlineStr">
+        <is>
+          <t>خرید و ملزومات</t>
+        </is>
+      </c>
+      <c r="E113" s="29" t="inlineStr">
+        <is>
+          <t>510203</t>
+        </is>
+      </c>
+      <c r="F113" s="30" t="inlineStr">
+        <is>
+          <t>تخفیفات نقدی خرید</t>
+        </is>
+      </c>
+      <c r="G113" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H113" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C114" s="27" t="inlineStr">
+        <is>
+          <t>5103</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>هزینه‌های مستقیم حمل و نقل</t>
+        </is>
+      </c>
+      <c r="E114" s="27" t="inlineStr"/>
+      <c r="F114" s="28" t="inlineStr"/>
+      <c r="G114" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H114" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A115" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B115" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C115" s="29" t="inlineStr">
+        <is>
+          <t>5103</t>
+        </is>
+      </c>
+      <c r="D115" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های مستقیم حمل و نقل</t>
+        </is>
+      </c>
+      <c r="E115" s="29" t="inlineStr">
+        <is>
+          <t>510301</t>
+        </is>
+      </c>
+      <c r="F115" s="30" t="inlineStr">
+        <is>
+          <t>هزینه حمل کالای خریداری شده</t>
+        </is>
+      </c>
+      <c r="G115" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H115" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A116" s="29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B116" s="30" t="inlineStr">
+        <is>
+          <t>بهای تمام شده کالای فروش رفته</t>
+        </is>
+      </c>
+      <c r="C116" s="29" t="inlineStr">
+        <is>
+          <t>5103</t>
+        </is>
+      </c>
+      <c r="D116" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های مستقیم حمل و نقل</t>
+        </is>
+      </c>
+      <c r="E116" s="29" t="inlineStr">
+        <is>
+          <t>510302</t>
+        </is>
+      </c>
+      <c r="F116" s="30" t="inlineStr">
+        <is>
+          <t>حقوق و عوارض گمرکی ترخیص کالا</t>
+        </is>
+      </c>
+      <c r="G116" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H116" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B117" s="26" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr"/>
+      <c r="D117" s="26" t="inlineStr"/>
+      <c r="E117" s="25" t="inlineStr"/>
+      <c r="F117" s="26" t="inlineStr"/>
+      <c r="G117" s="25" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H117" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B118" s="28" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C118" s="27" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D118" s="28" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E118" s="27" t="inlineStr"/>
+      <c r="F118" s="28" t="inlineStr"/>
+      <c r="G118" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H118" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A119" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B119" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C119" s="29" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D119" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E119" s="29" t="inlineStr">
+        <is>
+          <t>520101</t>
+        </is>
+      </c>
+      <c r="F119" s="30" t="inlineStr">
+        <is>
+          <t>حقوق پایه و حقوق ماهانه</t>
+        </is>
+      </c>
+      <c r="G119" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H119" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A120" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B120" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C120" s="29" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D120" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E120" s="29" t="inlineStr">
+        <is>
+          <t>520102</t>
+        </is>
+      </c>
+      <c r="F120" s="30" t="inlineStr">
+        <is>
+          <t>اضافه‌کاری و پاداش پرسنل</t>
+        </is>
+      </c>
+      <c r="G120" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H120" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A121" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B121" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C121" s="29" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D121" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E121" s="29" t="inlineStr">
+        <is>
+          <t>520103</t>
+        </is>
+      </c>
+      <c r="F121" s="30" t="inlineStr">
+        <is>
+          <t>حق بیمه سهم کارفرما</t>
+        </is>
+      </c>
+      <c r="G121" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H121" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A122" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B122" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C122" s="29" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D122" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E122" s="29" t="inlineStr">
+        <is>
+          <t>520104</t>
+        </is>
+      </c>
+      <c r="F122" s="30" t="inlineStr">
+        <is>
+          <t>بن و مسکن و اولاد پرسنل</t>
+        </is>
+      </c>
+      <c r="G122" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H122" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A123" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B123" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C123" s="29" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D123" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های حقوق و دستمزد</t>
+        </is>
+      </c>
+      <c r="E123" s="29" t="inlineStr">
+        <is>
+          <t>520105</t>
+        </is>
+      </c>
+      <c r="F123" s="30" t="inlineStr">
+        <is>
+          <t>عیدی و سنوات پایان سال</t>
+        </is>
+      </c>
+      <c r="G123" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H123" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B124" s="28" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C124" s="27" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D124" s="28" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E124" s="27" t="inlineStr"/>
+      <c r="F124" s="28" t="inlineStr"/>
+      <c r="G124" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H124" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A125" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B125" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C125" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D125" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E125" s="29" t="inlineStr">
+        <is>
+          <t>520201</t>
+        </is>
+      </c>
+      <c r="F125" s="30" t="inlineStr">
+        <is>
+          <t>هزینه اجاره دفتر و انبار</t>
+        </is>
+      </c>
+      <c r="G125" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H125" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A126" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B126" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C126" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D126" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E126" s="29" t="inlineStr">
+        <is>
+          <t>520202</t>
+        </is>
+      </c>
+      <c r="F126" s="30" t="inlineStr">
+        <is>
+          <t>هزینه آب، برق، گاز و تلفن</t>
+        </is>
+      </c>
+      <c r="G126" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H126" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A127" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B127" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C127" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D127" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E127" s="29" t="inlineStr">
+        <is>
+          <t>520203</t>
+        </is>
+      </c>
+      <c r="F127" s="30" t="inlineStr">
+        <is>
+          <t>هزینه ملزومات و لوازم‌التحریر</t>
+        </is>
+      </c>
+      <c r="G127" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H127" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A128" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B128" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D128" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E128" s="29" t="inlineStr">
+        <is>
+          <t>520204</t>
+        </is>
+      </c>
+      <c r="F128" s="30" t="inlineStr">
+        <is>
+          <t>هزینه ایاب و ذهاب و پذیرایی</t>
+        </is>
+      </c>
+      <c r="G128" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H128" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A129" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B129" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C129" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D129" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E129" s="29" t="inlineStr">
+        <is>
+          <t>520205</t>
+        </is>
+      </c>
+      <c r="F129" s="30" t="inlineStr">
+        <is>
+          <t>هزینه پست، پیک و ارتباطات</t>
+        </is>
+      </c>
+      <c r="G129" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H129" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A130" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B130" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D130" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E130" s="29" t="inlineStr">
+        <is>
+          <t>520206</t>
+        </is>
+      </c>
+      <c r="F130" s="30" t="inlineStr">
+        <is>
+          <t>هزینه تعمیر و نگهداری ساختمان و اثاثه</t>
+        </is>
+      </c>
+      <c r="G130" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H130" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A131" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B131" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C131" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D131" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E131" s="29" t="inlineStr">
+        <is>
+          <t>520207</t>
+        </is>
+      </c>
+      <c r="F131" s="30" t="inlineStr">
+        <is>
+          <t>هزینه بیمه اموال و دارایی‌ها</t>
+        </is>
+      </c>
+      <c r="G131" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H131" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A132" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B132" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C132" s="29" t="inlineStr">
+        <is>
+          <t>5202</t>
+        </is>
+      </c>
+      <c r="D132" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="E132" s="29" t="inlineStr">
+        <is>
+          <t>520208</t>
+        </is>
+      </c>
+      <c r="F132" s="30" t="inlineStr">
+        <is>
+          <t>حق‌الزحمه حسابرسی و مشاوره</t>
+        </is>
+      </c>
+      <c r="G132" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H132" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A133" s="27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B133" s="28" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C133" s="27" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="D133" s="28" t="inlineStr">
+        <is>
+          <t>هزینه‌های توزیع و فروش</t>
+        </is>
+      </c>
+      <c r="E133" s="27" t="inlineStr"/>
+      <c r="F133" s="28" t="inlineStr"/>
+      <c r="G133" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H133" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A134" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B134" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C134" s="29" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های توزیع و فروش</t>
+        </is>
+      </c>
+      <c r="E134" s="29" t="inlineStr">
+        <is>
+          <t>520301</t>
+        </is>
+      </c>
+      <c r="F134" s="30" t="inlineStr">
+        <is>
+          <t>هزینه تبلیغات و بازاریابی</t>
+        </is>
+      </c>
+      <c r="G134" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H134" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A135" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B135" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C135" s="29" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="D135" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های توزیع و فروش</t>
+        </is>
+      </c>
+      <c r="E135" s="29" t="inlineStr">
+        <is>
+          <t>520302</t>
+        </is>
+      </c>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>هزینه حمل و نقل فروش کالا</t>
+        </is>
+      </c>
+      <c r="G135" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H135" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A136" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B136" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C136" s="29" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="D136" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های توزیع و فروش</t>
+        </is>
+      </c>
+      <c r="E136" s="29" t="inlineStr">
+        <is>
+          <t>520303</t>
+        </is>
+      </c>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>هزینه پورسانت نمایندگی‌ها و بازاریابان</t>
+        </is>
+      </c>
+      <c r="G136" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H136" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B137" s="28" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C137" s="27" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="D137" s="28" t="inlineStr">
+        <is>
+          <t>هزینه‌های مالی</t>
+        </is>
+      </c>
+      <c r="E137" s="27" t="inlineStr"/>
+      <c r="F137" s="28" t="inlineStr"/>
+      <c r="G137" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H137" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A138" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B138" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C138" s="29" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="D138" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های مالی</t>
+        </is>
+      </c>
+      <c r="E138" s="29" t="inlineStr">
+        <is>
+          <t>520401</t>
+        </is>
+      </c>
+      <c r="F138" s="30" t="inlineStr">
+        <is>
+          <t>هزینه کارمزد بانکی</t>
+        </is>
+      </c>
+      <c r="G138" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H138" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A139" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B139" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C139" s="29" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="D139" s="30" t="inlineStr">
+        <is>
+          <t>هزینه‌های مالی</t>
+        </is>
+      </c>
+      <c r="E139" s="29" t="inlineStr">
+        <is>
+          <t>520402</t>
+        </is>
+      </c>
+      <c r="F139" s="30" t="inlineStr">
+        <is>
+          <t>هزینه سود و کارمزد تسهیلات بانکی</t>
+        </is>
+      </c>
+      <c r="G139" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H139" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B140" s="28" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C140" s="27" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="D140" s="28" t="inlineStr">
+        <is>
+          <t>هزینه استهلاک</t>
+        </is>
+      </c>
+      <c r="E140" s="27" t="inlineStr"/>
+      <c r="F140" s="28" t="inlineStr"/>
+      <c r="G140" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H140" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A141" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B141" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C141" s="29" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="D141" s="30" t="inlineStr">
+        <is>
+          <t>هزینه استهلاک</t>
+        </is>
+      </c>
+      <c r="E141" s="29" t="inlineStr">
+        <is>
+          <t>520501</t>
+        </is>
+      </c>
+      <c r="F141" s="30" t="inlineStr">
+        <is>
+          <t>هزینه استهلاک دارایی‌های ثابت مشهود</t>
+        </is>
+      </c>
+      <c r="G141" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H141" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A142" s="29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B142" s="30" t="inlineStr">
+        <is>
+          <t>هزینه های عمومی و اداری</t>
+        </is>
+      </c>
+      <c r="C142" s="29" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>هزینه استهلاک</t>
+        </is>
+      </c>
+      <c r="E142" s="29" t="inlineStr">
+        <is>
+          <t>520502</t>
+        </is>
+      </c>
+      <c r="F142" s="30" t="inlineStr">
+        <is>
+          <t>هزینه استهلاک دارایی‌های نامشهود</t>
+        </is>
+      </c>
+      <c r="G142" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H142" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="25" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B143" s="26" t="inlineStr">
+        <is>
+          <t>عملکرد و سود و زیان</t>
+        </is>
+      </c>
+      <c r="C143" s="25" t="inlineStr"/>
+      <c r="D143" s="26" t="inlineStr"/>
+      <c r="E143" s="25" t="inlineStr"/>
+      <c r="F143" s="26" t="inlineStr"/>
+      <c r="G143" s="25" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H143" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B144" s="28" t="inlineStr">
+        <is>
+          <t>عملکرد و سود و زیان</t>
+        </is>
+      </c>
+      <c r="C144" s="27" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="D144" s="28" t="inlineStr">
+        <is>
+          <t>حساب خلاصه سود و زیان</t>
+        </is>
+      </c>
+      <c r="E144" s="27" t="inlineStr"/>
+      <c r="F144" s="28" t="inlineStr"/>
+      <c r="G144" s="27" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H144" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A145" s="29" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B145" s="30" t="inlineStr">
+        <is>
+          <t>عملکرد و سود و زیان</t>
+        </is>
+      </c>
+      <c r="C145" s="29" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="D145" s="30" t="inlineStr">
+        <is>
+          <t>حساب خلاصه سود و زیان</t>
+        </is>
+      </c>
+      <c r="E145" s="29" t="inlineStr">
+        <is>
+          <t>610101</t>
+        </is>
+      </c>
+      <c r="F145" s="30" t="inlineStr">
+        <is>
+          <t>خلاصه سود و زیان سال جاری</t>
+        </is>
+      </c>
+      <c r="G145" s="29" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H145" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B146" s="28" t="inlineStr">
+        <is>
+          <t>عملکرد و سود و زیان</t>
+        </is>
+      </c>
+      <c r="C146" s="27" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="D146" s="28" t="inlineStr">
+        <is>
+          <t>تعدیلات سنواتی</t>
+        </is>
+      </c>
+      <c r="E146" s="27" t="inlineStr"/>
+      <c r="F146" s="28" t="inlineStr"/>
+      <c r="G146" s="27" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H146" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A147" s="29" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>عملکرد و سود و زیان</t>
+        </is>
+      </c>
+      <c r="C147" s="29" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <t>تعدیلات سنواتی</t>
+        </is>
+      </c>
+      <c r="E147" s="29" t="inlineStr">
+        <is>
+          <t>610201</t>
+        </is>
+      </c>
+      <c r="F147" s="30" t="inlineStr">
+        <is>
+          <t>تعدیلات سنواتی سود و زیان</t>
+        </is>
+      </c>
+      <c r="G147" s="29" t="inlineStr">
+        <is>
+          <t>مشترک</t>
+        </is>
+      </c>
+      <c r="H147" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="25" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B148" s="26" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C148" s="25" t="inlineStr"/>
+      <c r="D148" s="26" t="inlineStr"/>
+      <c r="E148" s="25" t="inlineStr"/>
+      <c r="F148" s="26" t="inlineStr"/>
+      <c r="G148" s="25" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H148" s="25" t="inlineStr">
+        <is>
+          <t>گروه</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B149" s="28" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="D149" s="28" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به نفع شرکت</t>
+        </is>
+      </c>
+      <c r="E149" s="27" t="inlineStr"/>
+      <c r="F149" s="28" t="inlineStr"/>
+      <c r="G149" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H149" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A150" s="29" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B150" s="30" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C150" s="29" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به نفع شرکت</t>
+        </is>
+      </c>
+      <c r="E150" s="29" t="inlineStr">
+        <is>
+          <t>710101</t>
+        </is>
+      </c>
+      <c r="F150" s="30" t="inlineStr">
+        <is>
+          <t>اسناد وثیقه‌ای و ضمانتی دریافتی</t>
+        </is>
+      </c>
+      <c r="G150" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H150" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A151" s="29" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C151" s="29" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="D151" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به نفع شرکت</t>
+        </is>
+      </c>
+      <c r="E151" s="29" t="inlineStr">
+        <is>
+          <t>710102</t>
+        </is>
+      </c>
+      <c r="F151" s="30" t="inlineStr">
+        <is>
+          <t>طرف حساب اسناد انتظامی دریافتی</t>
+        </is>
+      </c>
+      <c r="G151" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H151" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A152" s="27" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B152" s="28" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C152" s="27" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="D152" s="28" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به عهده شرکت</t>
+        </is>
+      </c>
+      <c r="E152" s="27" t="inlineStr"/>
+      <c r="F152" s="28" t="inlineStr"/>
+      <c r="G152" s="27" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H152" s="27" t="inlineStr">
+        <is>
+          <t>کل</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A153" s="29" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C153" s="29" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="D153" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به عهده شرکت</t>
+        </is>
+      </c>
+      <c r="E153" s="29" t="inlineStr">
+        <is>
+          <t>710201</t>
+        </is>
+      </c>
+      <c r="F153" s="30" t="inlineStr">
+        <is>
+          <t>اسناد وثیقه‌ای و ضمانتی پرداختی</t>
+        </is>
+      </c>
+      <c r="G153" s="29" t="inlineStr">
+        <is>
+          <t>بدهکار</t>
+        </is>
+      </c>
+      <c r="H153" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" outlineLevel="1" ht="20" customHeight="1">
+      <c r="A154" s="29" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>حسابهای انتظامی</t>
+        </is>
+      </c>
+      <c r="C154" s="29" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="D154" s="30" t="inlineStr">
+        <is>
+          <t>حساب‌های انتظامی به عهده شرکت</t>
+        </is>
+      </c>
+      <c r="E154" s="29" t="inlineStr">
+        <is>
+          <t>710202</t>
+        </is>
+      </c>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>طرف حساب اسناد انتظامی پرداختی</t>
+        </is>
+      </c>
+      <c r="G154" s="29" t="inlineStr">
+        <is>
+          <t>بستانکار</t>
+        </is>
+      </c>
+      <c r="H154" s="29" t="inlineStr">
+        <is>
+          <t>معین</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>